--- a/document/Webエンジニアスキル管理機能・非機能要件.xlsx
+++ b/document/Webエンジニアスキル管理機能・非機能要件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/317e370d51a78cda/Desktop/WEBスクール/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="213" documentId="11_AD4D066CA252ABDACC10488BE9D5EBD472EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECB97E9C-8329-4EF7-82D6-FA8CC8ED4704}"/>
+  <xr:revisionPtr revIDLastSave="217" documentId="11_AD4D066CA252ABDACC10488BE9D5EBD472EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4B459DD-8BB9-4864-95C2-E6969F8751B7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>【機能】</t>
     <phoneticPr fontId="1"/>
@@ -139,13 +139,6 @@
     <t>スキル履歴検索</t>
     <rPh sb="3" eb="5">
       <t>リレキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スキル削除</t>
-    <rPh sb="3" eb="5">
-      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -342,16 +335,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -362,8 +358,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -691,19 +693,19 @@
       <c r="AD6" t="s">
         <v>11</v>
       </c>
-      <c r="AJ6" s="7" t="s">
+      <c r="AJ6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AK6" s="7"/>
-      <c r="AL6" s="7"/>
-      <c r="AM6" s="7"/>
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="1"/>
+      <c r="AM6" s="1"/>
       <c r="AN6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="AO6" s="2"/>
       <c r="AP6" s="2"/>
       <c r="AQ6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AR6" s="2"/>
       <c r="AS6" s="2"/>
@@ -750,10 +752,10 @@
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
-      <c r="AJ7" s="7"/>
-      <c r="AK7" s="7"/>
-      <c r="AL7" s="7"/>
-      <c r="AM7" s="7"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="1"/>
       <c r="AN7" s="2" t="s">
         <v>14</v>
       </c>
@@ -921,30 +923,30 @@
       <c r="BH11" s="3"/>
     </row>
     <row r="12" spans="3:60">
-      <c r="D12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="s">
+      <c r="D12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="10"/>
       <c r="AJ12" s="2" t="s">
         <v>2</v>
       </c>
@@ -962,7 +964,7 @@
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AW12" s="2"/>
       <c r="AX12" s="2"/>
@@ -979,7 +981,7 @@
     </row>
     <row r="13" spans="3:60">
       <c r="D13" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -1003,7 +1005,7 @@
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
       <c r="AJ13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK13" s="2"/>
       <c r="AL13" s="2"/>
@@ -1011,7 +1013,7 @@
       <c r="AN13" s="2"/>
       <c r="AO13" s="2"/>
       <c r="AP13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ13" s="2"/>
       <c r="AR13" s="2"/>
@@ -1019,7 +1021,7 @@
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW13" s="2"/>
       <c r="AX13" s="2"/>
@@ -1035,32 +1037,8 @@
       <c r="BH13" s="2"/>
     </row>
     <row r="14" spans="3:60">
-      <c r="D14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
       <c r="AJ14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK14" s="2"/>
       <c r="AL14" s="2"/>
@@ -1068,7 +1046,7 @@
       <c r="AN14" s="2"/>
       <c r="AO14" s="2"/>
       <c r="AP14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AQ14" s="2"/>
       <c r="AR14" s="2"/>
@@ -1076,7 +1054,7 @@
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW14" s="2"/>
       <c r="AX14" s="2"/>
@@ -1101,7 +1079,7 @@
       <c r="AN15" s="2"/>
       <c r="AO15" s="2"/>
       <c r="AP15" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ15" s="2"/>
       <c r="AR15" s="2"/>
@@ -1109,7 +1087,7 @@
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW15" s="2"/>
       <c r="AX15" s="2"/>
@@ -1126,12 +1104,12 @@
     </row>
     <row r="18" spans="30:60">
       <c r="AD18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="30:60">
       <c r="AJ20" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
@@ -1142,119 +1120,119 @@
       <c r="AQ20" s="3"/>
       <c r="AR20" s="3"/>
       <c r="AS20" s="3"/>
-      <c r="AT20" s="4" t="s">
+      <c r="AT20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AU20" s="6"/>
+      <c r="AV20" s="6"/>
+      <c r="AW20" s="6"/>
+      <c r="AX20" s="6"/>
+      <c r="AY20" s="6"/>
+      <c r="AZ20" s="6"/>
+      <c r="BA20" s="6"/>
+      <c r="BB20" s="6"/>
+      <c r="BC20" s="6"/>
+      <c r="BD20" s="6"/>
+      <c r="BE20" s="6"/>
+      <c r="BF20" s="6"/>
+      <c r="BG20" s="6"/>
+      <c r="BH20" s="7"/>
+    </row>
+    <row r="21" spans="30:60">
+      <c r="AJ21" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AU20" s="5"/>
-      <c r="AV20" s="5"/>
-      <c r="AW20" s="5"/>
-      <c r="AX20" s="5"/>
-      <c r="AY20" s="5"/>
-      <c r="AZ20" s="5"/>
-      <c r="BA20" s="5"/>
-      <c r="BB20" s="5"/>
-      <c r="BC20" s="5"/>
-      <c r="BD20" s="5"/>
-      <c r="BE20" s="5"/>
-      <c r="BF20" s="5"/>
-      <c r="BG20" s="5"/>
-      <c r="BH20" s="6"/>
-    </row>
-    <row r="21" spans="30:60">
-      <c r="AJ21" s="1" t="s">
+      <c r="AK21" s="4"/>
+      <c r="AL21" s="4"/>
+      <c r="AM21" s="4"/>
+      <c r="AN21" s="4"/>
+      <c r="AO21" s="4"/>
+      <c r="AP21" s="4"/>
+      <c r="AQ21" s="4"/>
+      <c r="AR21" s="4"/>
+      <c r="AS21" s="4"/>
+      <c r="AT21" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AK21" s="1"/>
-      <c r="AL21" s="1"/>
-      <c r="AM21" s="1"/>
-      <c r="AN21" s="1"/>
-      <c r="AO21" s="1"/>
-      <c r="AP21" s="1"/>
-      <c r="AQ21" s="1"/>
-      <c r="AR21" s="1"/>
-      <c r="AS21" s="1"/>
-      <c r="AT21" s="1" t="s">
+      <c r="AU21" s="4"/>
+      <c r="AV21" s="4"/>
+      <c r="AW21" s="4"/>
+      <c r="AX21" s="4"/>
+      <c r="AY21" s="4"/>
+      <c r="AZ21" s="4"/>
+      <c r="BA21" s="4"/>
+      <c r="BB21" s="4"/>
+      <c r="BC21" s="4"/>
+      <c r="BD21" s="4"/>
+      <c r="BE21" s="4"/>
+      <c r="BF21" s="4"/>
+      <c r="BG21" s="4"/>
+      <c r="BH21" s="4"/>
+    </row>
+    <row r="22" spans="30:60">
+      <c r="AJ22" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="AU21" s="1"/>
-      <c r="AV21" s="1"/>
-      <c r="AW21" s="1"/>
-      <c r="AX21" s="1"/>
-      <c r="AY21" s="1"/>
-      <c r="AZ21" s="1"/>
-      <c r="BA21" s="1"/>
-      <c r="BB21" s="1"/>
-      <c r="BC21" s="1"/>
-      <c r="BD21" s="1"/>
-      <c r="BE21" s="1"/>
-      <c r="BF21" s="1"/>
-      <c r="BG21" s="1"/>
-      <c r="BH21" s="1"/>
-    </row>
-    <row r="22" spans="30:60">
-      <c r="AJ22" s="1" t="s">
+      <c r="AK22" s="4"/>
+      <c r="AL22" s="4"/>
+      <c r="AM22" s="4"/>
+      <c r="AN22" s="4"/>
+      <c r="AO22" s="4"/>
+      <c r="AP22" s="4"/>
+      <c r="AQ22" s="4"/>
+      <c r="AR22" s="4"/>
+      <c r="AS22" s="4"/>
+      <c r="AT22" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AK22" s="1"/>
-      <c r="AL22" s="1"/>
-      <c r="AM22" s="1"/>
-      <c r="AN22" s="1"/>
-      <c r="AO22" s="1"/>
-      <c r="AP22" s="1"/>
-      <c r="AQ22" s="1"/>
-      <c r="AR22" s="1"/>
-      <c r="AS22" s="1"/>
-      <c r="AT22" s="1" t="s">
+      <c r="AU22" s="4"/>
+      <c r="AV22" s="4"/>
+      <c r="AW22" s="4"/>
+      <c r="AX22" s="4"/>
+      <c r="AY22" s="4"/>
+      <c r="AZ22" s="4"/>
+      <c r="BA22" s="4"/>
+      <c r="BB22" s="4"/>
+      <c r="BC22" s="4"/>
+      <c r="BD22" s="4"/>
+      <c r="BE22" s="4"/>
+      <c r="BF22" s="4"/>
+      <c r="BG22" s="4"/>
+      <c r="BH22" s="4"/>
+    </row>
+    <row r="23" spans="30:60">
+      <c r="AJ23" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AU22" s="1"/>
-      <c r="AV22" s="1"/>
-      <c r="AW22" s="1"/>
-      <c r="AX22" s="1"/>
-      <c r="AY22" s="1"/>
-      <c r="AZ22" s="1"/>
-      <c r="BA22" s="1"/>
-      <c r="BB22" s="1"/>
-      <c r="BC22" s="1"/>
-      <c r="BD22" s="1"/>
-      <c r="BE22" s="1"/>
-      <c r="BF22" s="1"/>
-      <c r="BG22" s="1"/>
-      <c r="BH22" s="1"/>
-    </row>
-    <row r="23" spans="30:60">
-      <c r="AJ23" s="1" t="s">
+      <c r="AK23" s="4"/>
+      <c r="AL23" s="4"/>
+      <c r="AM23" s="4"/>
+      <c r="AN23" s="4"/>
+      <c r="AO23" s="4"/>
+      <c r="AP23" s="4"/>
+      <c r="AQ23" s="4"/>
+      <c r="AR23" s="4"/>
+      <c r="AS23" s="4"/>
+      <c r="AT23" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AK23" s="1"/>
-      <c r="AL23" s="1"/>
-      <c r="AM23" s="1"/>
-      <c r="AN23" s="1"/>
-      <c r="AO23" s="1"/>
-      <c r="AP23" s="1"/>
-      <c r="AQ23" s="1"/>
-      <c r="AR23" s="1"/>
-      <c r="AS23" s="1"/>
-      <c r="AT23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AU23" s="1"/>
-      <c r="AV23" s="1"/>
-      <c r="AW23" s="1"/>
-      <c r="AX23" s="1"/>
-      <c r="AY23" s="1"/>
-      <c r="AZ23" s="1"/>
-      <c r="BA23" s="1"/>
-      <c r="BB23" s="1"/>
-      <c r="BC23" s="1"/>
-      <c r="BD23" s="1"/>
-      <c r="BE23" s="1"/>
-      <c r="BF23" s="1"/>
-      <c r="BG23" s="1"/>
-      <c r="BH23" s="1"/>
+      <c r="AU23" s="4"/>
+      <c r="AV23" s="4"/>
+      <c r="AW23" s="4"/>
+      <c r="AX23" s="4"/>
+      <c r="AY23" s="4"/>
+      <c r="AZ23" s="4"/>
+      <c r="BA23" s="4"/>
+      <c r="BB23" s="4"/>
+      <c r="BC23" s="4"/>
+      <c r="BD23" s="4"/>
+      <c r="BE23" s="4"/>
+      <c r="BF23" s="4"/>
+      <c r="BG23" s="4"/>
+      <c r="BH23" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="52">
     <mergeCell ref="AQ6:BH6"/>
     <mergeCell ref="AQ7:BH7"/>
     <mergeCell ref="AP15:AU15"/>
@@ -1273,17 +1251,15 @@
     <mergeCell ref="AJ14:AO14"/>
     <mergeCell ref="AJ15:AO15"/>
     <mergeCell ref="R11:W11"/>
+    <mergeCell ref="R13:W13"/>
     <mergeCell ref="R12:W12"/>
+    <mergeCell ref="AJ13:AO13"/>
+    <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="D12:K12"/>
+    <mergeCell ref="D13:K13"/>
+    <mergeCell ref="D11:K11"/>
     <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="D13:K13"/>
-    <mergeCell ref="D14:K14"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="L14:Q14"/>
     <mergeCell ref="L11:Q11"/>
-    <mergeCell ref="L12:Q12"/>
-    <mergeCell ref="R14:W14"/>
-    <mergeCell ref="R13:W13"/>
     <mergeCell ref="D6:K6"/>
     <mergeCell ref="L6:Q6"/>
     <mergeCell ref="R6:W6"/>
@@ -1309,7 +1285,6 @@
     <mergeCell ref="AN7:AP7"/>
     <mergeCell ref="AJ11:AO11"/>
     <mergeCell ref="AJ12:AO12"/>
-    <mergeCell ref="AJ13:AO13"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
